--- a/manage/[커리큘럼] SK네트웍스 Family AI 캠프 21기.xlsx
+++ b/manage/[커리큘럼] SK네트웍스 Family AI 캠프 21기.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\py_repo\skn21\manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F3CAAE-81AA-4FB1-941A-A4D3C2A1A0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8120F511-5EDC-4700-95D0-C65469AED0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11655" yWindow="0" windowWidth="15825" windowHeight="15563" tabRatio="436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="3435" windowWidth="16560" windowHeight="11775" tabRatio="436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="커리큘럼" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="105">
   <si>
     <t xml:space="preserve"> SK네트웍스 Family AI 캠프 21기 커리큘럼</t>
   </si>
@@ -837,6 +837,22 @@
         <charset val="129"/>
       </rPr>
       <t>첫번째딥러닝</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자연어</t>
     </r>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
@@ -3060,7 +3076,9 @@
       <c r="E39" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="36"/>
+      <c r="F39" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -3088,7 +3106,9 @@
       <c r="E40" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="36"/>
+      <c r="F40" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -3121,7 +3141,9 @@
       <c r="E41" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="36"/>
+      <c r="F41" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -3154,7 +3176,9 @@
       <c r="E42" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="36"/>
+      <c r="F42" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -3187,7 +3211,9 @@
       <c r="E43" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="36"/>
+      <c r="F43" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -3220,7 +3246,9 @@
       <c r="E44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="36"/>
+      <c r="F44" s="36" t="s">
+        <v>104</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
